--- a/data/WP18/WP18_auswertung_sachgebiete.xlsx
+++ b/data/WP18/WP18_auswertung_sachgebiete.xlsx
@@ -928,16 +928,16 @@
         <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="D6" t="n">
-        <v>35.7906458797327</v>
+        <v>35.8012698412698</v>
       </c>
       <c r="E6" t="n">
         <v>356</v>
       </c>
       <c r="F6" t="n">
-        <v>20.7126948775056</v>
+        <v>20.8888888888889</v>
       </c>
     </row>
     <row r="7">
@@ -4154,13 +4154,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{143E7E9B-054F-46B7-BE5A-B4F7F537C155}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D20B2F4E-A985-4B50-9FB1-9CBB73E96E56}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{44AB9726-CB77-4AD0-B917-0B9CA1838BB4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73294184-E9D1-4DCD-9C7E-8175A03869C0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8350488E-9D8D-4311-A53C-01822CF89400}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F815A132-BD60-4ABF-A284-57A91583D282}"/>
 </file>
--- a/data/WP18/WP18_auswertung_sachgebiete.xlsx
+++ b/data/WP18/WP18_auswertung_sachgebiete.xlsx
@@ -851,13 +851,13 @@
         <v>1796</v>
       </c>
       <c r="D2" t="n">
-        <v>37.1464365256125</v>
+        <v>36.8541202672606</v>
       </c>
       <c r="E2" t="n">
-        <v>1451</v>
+        <v>1404</v>
       </c>
       <c r="F2" t="n">
-        <v>19.2093541202673</v>
+        <v>21.826280623608</v>
       </c>
     </row>
     <row r="3">
@@ -871,13 +871,13 @@
         <v>759</v>
       </c>
       <c r="D3" t="n">
-        <v>39.6245059288538</v>
+        <v>39.3333333333333</v>
       </c>
       <c r="E3" t="n">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="F3" t="n">
-        <v>16.0737812911726</v>
+        <v>16.8642951251647</v>
       </c>
     </row>
     <row r="4">
@@ -891,13 +891,13 @@
         <v>579</v>
       </c>
       <c r="D4" t="n">
-        <v>35.8842832469775</v>
+        <v>35.6943005181347</v>
       </c>
       <c r="E4" t="n">
-        <v>490</v>
+        <v>483</v>
       </c>
       <c r="F4" t="n">
-        <v>15.3713298791019</v>
+        <v>16.580310880829</v>
       </c>
     </row>
     <row r="5">
@@ -911,13 +911,13 @@
         <v>517</v>
       </c>
       <c r="D5" t="n">
-        <v>34.6034816247582</v>
+        <v>34.137330754352</v>
       </c>
       <c r="E5" t="n">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="F5" t="n">
-        <v>40.0386847195358</v>
+        <v>41.1992263056093</v>
       </c>
     </row>
     <row r="6">
@@ -931,13 +931,13 @@
         <v>450</v>
       </c>
       <c r="D6" t="n">
-        <v>35.8012698412698</v>
+        <v>35.5288888888889</v>
       </c>
       <c r="E6" t="n">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F6" t="n">
-        <v>20.8888888888889</v>
+        <v>21.1111111111111</v>
       </c>
     </row>
     <row r="7">
@@ -951,13 +951,13 @@
         <v>395</v>
       </c>
       <c r="D7" t="n">
-        <v>39.9493670886076</v>
+        <v>39.1240506329114</v>
       </c>
       <c r="E7" t="n">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="F7" t="n">
-        <v>17.2151898734177</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -971,13 +971,13 @@
         <v>368</v>
       </c>
       <c r="D8" t="n">
-        <v>35.7336956521739</v>
+        <v>35.8097826086956</v>
       </c>
       <c r="E8" t="n">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F8" t="n">
-        <v>15.4891304347826</v>
+        <v>15.7608695652174</v>
       </c>
     </row>
     <row r="9">
@@ -991,13 +991,13 @@
         <v>362</v>
       </c>
       <c r="D9" t="n">
-        <v>34.878453038674</v>
+        <v>32.8121546961326</v>
       </c>
       <c r="E9" t="n">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="F9" t="n">
-        <v>30.110497237569</v>
+        <v>36.46408839779</v>
       </c>
     </row>
     <row r="10">
@@ -1011,13 +1011,13 @@
         <v>352</v>
       </c>
       <c r="D10" t="n">
-        <v>37.6619318181818</v>
+        <v>36.4375</v>
       </c>
       <c r="E10" t="n">
-        <v>281</v>
+        <v>263</v>
       </c>
       <c r="F10" t="n">
-        <v>20.1704545454545</v>
+        <v>25.2840909090909</v>
       </c>
     </row>
     <row r="11">
@@ -1031,13 +1031,13 @@
         <v>306</v>
       </c>
       <c r="D11" t="n">
-        <v>38.6209150326797</v>
+        <v>38.9019607843137</v>
       </c>
       <c r="E11" t="n">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="F11" t="n">
-        <v>16.9934640522876</v>
+        <v>17.3202614379085</v>
       </c>
     </row>
     <row r="12">
@@ -1051,13 +1051,13 @@
         <v>234</v>
       </c>
       <c r="D12" t="n">
-        <v>30.7606837606838</v>
+        <v>30.4700854700855</v>
       </c>
       <c r="E12" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F12" t="n">
-        <v>61.5384615384615</v>
+        <v>61.965811965812</v>
       </c>
     </row>
     <row r="13">
@@ -1071,13 +1071,13 @@
         <v>203</v>
       </c>
       <c r="D13" t="n">
-        <v>31.8669950738916</v>
+        <v>30.5566502463054</v>
       </c>
       <c r="E13" t="n">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="F13" t="n">
-        <v>30.0492610837438</v>
+        <v>35.4679802955665</v>
       </c>
     </row>
     <row r="14">
@@ -1091,13 +1091,13 @@
         <v>199</v>
       </c>
       <c r="D14" t="n">
-        <v>31.0603015075377</v>
+        <v>30.4723618090452</v>
       </c>
       <c r="E14" t="n">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F14" t="n">
-        <v>52.7638190954774</v>
+        <v>54.2713567839196</v>
       </c>
     </row>
     <row r="15">
@@ -1111,13 +1111,13 @@
         <v>187</v>
       </c>
       <c r="D15" t="n">
-        <v>36.2994652406417</v>
+        <v>35.5882352941176</v>
       </c>
       <c r="E15" t="n">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="F15" t="n">
-        <v>22.4598930481284</v>
+        <v>28.3422459893048</v>
       </c>
     </row>
     <row r="16">
@@ -1131,13 +1131,13 @@
         <v>182</v>
       </c>
       <c r="D16" t="n">
-        <v>32.6098901098901</v>
+        <v>32.0384615384615</v>
       </c>
       <c r="E16" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="F16" t="n">
-        <v>32.967032967033</v>
+        <v>41.7582417582418</v>
       </c>
     </row>
     <row r="17">
@@ -1151,13 +1151,13 @@
         <v>176</v>
       </c>
       <c r="D17" t="n">
-        <v>34.5738636363636</v>
+        <v>34.3181818181818</v>
       </c>
       <c r="E17" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F17" t="n">
-        <v>22.7272727272727</v>
+        <v>24.4318181818182</v>
       </c>
     </row>
     <row r="18">
@@ -1171,13 +1171,13 @@
         <v>148</v>
       </c>
       <c r="D18" t="n">
-        <v>34.2702702702703</v>
+        <v>33.222972972973</v>
       </c>
       <c r="E18" t="n">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="F18" t="n">
-        <v>25.6756756756757</v>
+        <v>34.4594594594595</v>
       </c>
     </row>
     <row r="19">
@@ -1191,13 +1191,13 @@
         <v>135</v>
       </c>
       <c r="D19" t="n">
-        <v>29.562962962963</v>
+        <v>29.0518518518519</v>
       </c>
       <c r="E19" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F19" t="n">
-        <v>47.4074074074074</v>
+        <v>48.8888888888889</v>
       </c>
     </row>
     <row r="20">
@@ -1211,13 +1211,13 @@
         <v>133</v>
       </c>
       <c r="D20" t="n">
-        <v>31.7218045112782</v>
+        <v>30.6616541353383</v>
       </c>
       <c r="E20" t="n">
-        <v>99</v>
+        <v>80</v>
       </c>
       <c r="F20" t="n">
-        <v>25.5639097744361</v>
+        <v>39.8496240601504</v>
       </c>
     </row>
     <row r="21">
@@ -1231,13 +1231,13 @@
         <v>131</v>
       </c>
       <c r="D21" t="n">
-        <v>37.3511450381679</v>
+        <v>36.9160305343511</v>
       </c>
       <c r="E21" t="n">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F21" t="n">
-        <v>18.3206106870229</v>
+        <v>22.9007633587786</v>
       </c>
     </row>
     <row r="22">
@@ -1251,13 +1251,13 @@
         <v>128</v>
       </c>
       <c r="D22" t="n">
-        <v>31.2734375</v>
+        <v>30.1484375</v>
       </c>
       <c r="E22" t="n">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F22" t="n">
-        <v>28.90625</v>
+        <v>32.8125</v>
       </c>
     </row>
     <row r="23">
@@ -1271,7 +1271,7 @@
         <v>128</v>
       </c>
       <c r="D23" t="n">
-        <v>40.7421875</v>
+        <v>40.546875</v>
       </c>
       <c r="E23" t="n">
         <v>117</v>
@@ -1291,13 +1291,13 @@
         <v>127</v>
       </c>
       <c r="D24" t="n">
-        <v>37.4251968503937</v>
+        <v>37.1338582677165</v>
       </c>
       <c r="E24" t="n">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F24" t="n">
-        <v>17.3228346456693</v>
+        <v>18.8976377952756</v>
       </c>
     </row>
     <row r="25">
@@ -1311,13 +1311,13 @@
         <v>124</v>
       </c>
       <c r="D25" t="n">
-        <v>40.2258064516129</v>
+        <v>39.9516129032258</v>
       </c>
       <c r="E25" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F25" t="n">
-        <v>11.2903225806452</v>
+        <v>12.0967741935484</v>
       </c>
     </row>
     <row r="26">
@@ -1331,13 +1331,13 @@
         <v>117</v>
       </c>
       <c r="D26" t="n">
-        <v>35.2307692307692</v>
+        <v>34.6666666666667</v>
       </c>
       <c r="E26" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F26" t="n">
-        <v>10.2564102564102</v>
+        <v>14.5299145299145</v>
       </c>
     </row>
     <row r="27">
@@ -1351,7 +1351,7 @@
         <v>113</v>
       </c>
       <c r="D27" t="n">
-        <v>33.8761061946903</v>
+        <v>33.6548672566372</v>
       </c>
       <c r="E27" t="n">
         <v>90</v>
@@ -1371,13 +1371,13 @@
         <v>110</v>
       </c>
       <c r="D28" t="n">
-        <v>35.6090909090909</v>
+        <v>35.2909090909091</v>
       </c>
       <c r="E28" t="n">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F28" t="n">
-        <v>23.6363636363636</v>
+        <v>26.3636363636364</v>
       </c>
     </row>
     <row r="29">
@@ -1391,13 +1391,13 @@
         <v>97</v>
       </c>
       <c r="D29" t="n">
-        <v>34.360824742268</v>
+        <v>34.2577319587629</v>
       </c>
       <c r="E29" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F29" t="n">
-        <v>23.7113402061856</v>
+        <v>25.7731958762887</v>
       </c>
     </row>
     <row r="30">
@@ -1411,13 +1411,13 @@
         <v>96</v>
       </c>
       <c r="D30" t="n">
-        <v>34.7395833333333</v>
+        <v>34.4479166666667</v>
       </c>
       <c r="E30" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F30" t="n">
-        <v>26.0416666666667</v>
+        <v>29.1666666666667</v>
       </c>
     </row>
     <row r="31">
@@ -1431,13 +1431,13 @@
         <v>95</v>
       </c>
       <c r="D31" t="n">
-        <v>36.5894736842105</v>
+        <v>35.7578947368421</v>
       </c>
       <c r="E31" t="n">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="F31" t="n">
-        <v>15.7894736842105</v>
+        <v>22.1052631578947</v>
       </c>
     </row>
     <row r="32">
@@ -1451,7 +1451,7 @@
         <v>95</v>
       </c>
       <c r="D32" t="n">
-        <v>32.5157894736842</v>
+        <v>32.5578947368421</v>
       </c>
       <c r="E32" t="n">
         <v>59</v>
@@ -1471,13 +1471,13 @@
         <v>93</v>
       </c>
       <c r="D33" t="n">
-        <v>35.3978494623656</v>
+        <v>35.1397849462366</v>
       </c>
       <c r="E33" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F33" t="n">
-        <v>23.6559139784946</v>
+        <v>25.8064516129032</v>
       </c>
     </row>
     <row r="34">
@@ -1491,13 +1491,13 @@
         <v>91</v>
       </c>
       <c r="D34" t="n">
-        <v>40.4175824175824</v>
+        <v>38.6373626373626</v>
       </c>
       <c r="E34" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F34" t="n">
-        <v>20.8791208791209</v>
+        <v>23.0769230769231</v>
       </c>
     </row>
     <row r="35">
@@ -1511,13 +1511,13 @@
         <v>90</v>
       </c>
       <c r="D35" t="n">
-        <v>35.0666666666667</v>
+        <v>34.9444444444444</v>
       </c>
       <c r="E35" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F35" t="n">
-        <v>11.1111111111111</v>
+        <v>12.2222222222222</v>
       </c>
     </row>
     <row r="36">
@@ -1531,13 +1531,13 @@
         <v>89</v>
       </c>
       <c r="D36" t="n">
-        <v>31.0898876404494</v>
+        <v>30.1460674157303</v>
       </c>
       <c r="E36" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="F36" t="n">
-        <v>47.1910112359551</v>
+        <v>57.3033707865169</v>
       </c>
     </row>
     <row r="37">
@@ -1551,13 +1551,13 @@
         <v>89</v>
       </c>
       <c r="D37" t="n">
-        <v>33.2134831460674</v>
+        <v>32.6741573033708</v>
       </c>
       <c r="E37" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F37" t="n">
-        <v>20.2247191011236</v>
+        <v>24.7191011235955</v>
       </c>
     </row>
     <row r="38">
@@ -1571,13 +1571,13 @@
         <v>88</v>
       </c>
       <c r="D38" t="n">
-        <v>37.0795454545455</v>
+        <v>36.4886363636364</v>
       </c>
       <c r="E38" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F38" t="n">
-        <v>20.4545454545455</v>
+        <v>25</v>
       </c>
     </row>
     <row r="39">
@@ -1591,13 +1591,13 @@
         <v>87</v>
       </c>
       <c r="D39" t="n">
-        <v>29.8275862068966</v>
+        <v>29.4367816091954</v>
       </c>
       <c r="E39" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F39" t="n">
-        <v>73.5632183908046</v>
+        <v>72.4137931034483</v>
       </c>
     </row>
     <row r="40">
@@ -1611,13 +1611,13 @@
         <v>85</v>
       </c>
       <c r="D40" t="n">
-        <v>34.1764705882353</v>
+        <v>33.6941176470588</v>
       </c>
       <c r="E40" t="n">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="F40" t="n">
-        <v>20</v>
+        <v>27.0588235294118</v>
       </c>
     </row>
     <row r="41">
@@ -1631,7 +1631,7 @@
         <v>83</v>
       </c>
       <c r="D41" t="n">
-        <v>33.7710843373494</v>
+        <v>33.6385542168675</v>
       </c>
       <c r="E41" t="n">
         <v>58</v>
@@ -1651,13 +1651,13 @@
         <v>83</v>
       </c>
       <c r="D42" t="n">
-        <v>29.566265060241</v>
+        <v>28.9036144578313</v>
       </c>
       <c r="E42" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F42" t="n">
-        <v>75.9036144578313</v>
+        <v>74.6987951807229</v>
       </c>
     </row>
     <row r="43">
@@ -1671,7 +1671,7 @@
         <v>82</v>
       </c>
       <c r="D43" t="n">
-        <v>40.5487804878049</v>
+        <v>40.4146341463415</v>
       </c>
       <c r="E43" t="n">
         <v>78</v>
@@ -1691,13 +1691,13 @@
         <v>81</v>
       </c>
       <c r="D44" t="n">
-        <v>37.4074074074074</v>
+        <v>37.0493827160494</v>
       </c>
       <c r="E44" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F44" t="n">
-        <v>17.283950617284</v>
+        <v>18.5185185185185</v>
       </c>
     </row>
     <row r="45">
@@ -1711,13 +1711,13 @@
         <v>78</v>
       </c>
       <c r="D45" t="n">
-        <v>34.3461538461538</v>
+        <v>34.0897435897436</v>
       </c>
       <c r="E45" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="F45" t="n">
-        <v>24.3589743589744</v>
+        <v>30.7692307692308</v>
       </c>
     </row>
     <row r="46">
@@ -1731,13 +1731,13 @@
         <v>78</v>
       </c>
       <c r="D46" t="n">
-        <v>35.9871794871795</v>
+        <v>34.8589743589744</v>
       </c>
       <c r="E46" t="n">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="F46" t="n">
-        <v>23.0769230769231</v>
+        <v>32.051282051282</v>
       </c>
     </row>
     <row r="47">
@@ -1751,13 +1751,13 @@
         <v>77</v>
       </c>
       <c r="D47" t="n">
-        <v>36.1948051948052</v>
+        <v>36.025974025974</v>
       </c>
       <c r="E47" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F47" t="n">
-        <v>22.0779220779221</v>
+        <v>24.6753246753247</v>
       </c>
     </row>
     <row r="48">
@@ -1771,13 +1771,13 @@
         <v>76</v>
       </c>
       <c r="D48" t="n">
-        <v>36.1842105263158</v>
+        <v>35.75</v>
       </c>
       <c r="E48" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F48" t="n">
-        <v>36.8421052631579</v>
+        <v>39.4736842105263</v>
       </c>
     </row>
     <row r="49">
@@ -1791,13 +1791,13 @@
         <v>72</v>
       </c>
       <c r="D49" t="n">
-        <v>34.8472222222222</v>
+        <v>34.8888888888889</v>
       </c>
       <c r="E49" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F49" t="n">
-        <v>18.0555555555556</v>
+        <v>19.4444444444444</v>
       </c>
     </row>
     <row r="50">
@@ -1811,7 +1811,7 @@
         <v>68</v>
       </c>
       <c r="D50" t="n">
-        <v>35.7058823529412</v>
+        <v>35.1617647058824</v>
       </c>
       <c r="E50" t="n">
         <v>57</v>
@@ -1831,13 +1831,13 @@
         <v>67</v>
       </c>
       <c r="D51" t="n">
-        <v>40.7611940298507</v>
+        <v>40.5074626865672</v>
       </c>
       <c r="E51" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F51" t="n">
-        <v>8.95522388059702</v>
+        <v>11.9402985074627</v>
       </c>
     </row>
     <row r="52">
@@ -1851,13 +1851,13 @@
         <v>62</v>
       </c>
       <c r="D52" t="n">
-        <v>33.3709677419355</v>
+        <v>33.2258064516129</v>
       </c>
       <c r="E52" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F52" t="n">
-        <v>32.258064516129</v>
+        <v>30.6451612903226</v>
       </c>
     </row>
     <row r="53">
@@ -1871,13 +1871,13 @@
         <v>60</v>
       </c>
       <c r="D53" t="n">
-        <v>36.5333333333333</v>
+        <v>35.5833333333333</v>
       </c>
       <c r="E53" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F53" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="54">
@@ -1894,10 +1894,10 @@
         <v>37.2333333333333</v>
       </c>
       <c r="E54" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F54" t="n">
-        <v>10</v>
+        <v>11.6666666666667</v>
       </c>
     </row>
     <row r="55">
@@ -1911,7 +1911,7 @@
         <v>56</v>
       </c>
       <c r="D55" t="n">
-        <v>37.6607142857143</v>
+        <v>37.3928571428571</v>
       </c>
       <c r="E55" t="n">
         <v>43</v>
@@ -1931,7 +1931,7 @@
         <v>56</v>
       </c>
       <c r="D56" t="n">
-        <v>37.2857142857143</v>
+        <v>36.9285714285714</v>
       </c>
       <c r="E56" t="n">
         <v>47</v>
@@ -1951,13 +1951,13 @@
         <v>53</v>
       </c>
       <c r="D57" t="n">
-        <v>31.3207547169811</v>
+        <v>29.9622641509434</v>
       </c>
       <c r="E57" t="n">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="F57" t="n">
-        <v>35.8490566037736</v>
+        <v>49.0566037735849</v>
       </c>
     </row>
     <row r="58">
@@ -1971,13 +1971,13 @@
         <v>52</v>
       </c>
       <c r="D58" t="n">
-        <v>33.5769230769231</v>
+        <v>33.1730769230769</v>
       </c>
       <c r="E58" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F58" t="n">
-        <v>26.9230769230769</v>
+        <v>30.7692307692308</v>
       </c>
     </row>
     <row r="59">
@@ -1991,7 +1991,7 @@
         <v>50</v>
       </c>
       <c r="D59" t="n">
-        <v>37.58</v>
+        <v>37.16</v>
       </c>
       <c r="E59" t="n">
         <v>45</v>
@@ -2011,13 +2011,13 @@
         <v>49</v>
       </c>
       <c r="D60" t="n">
-        <v>38.7959183673469</v>
+        <v>38.3469387755102</v>
       </c>
       <c r="E60" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F60" t="n">
-        <v>22.4489795918367</v>
+        <v>30.6122448979592</v>
       </c>
     </row>
     <row r="61">
@@ -2031,13 +2031,13 @@
         <v>49</v>
       </c>
       <c r="D61" t="n">
-        <v>35.530612244898</v>
+        <v>35.3469387755102</v>
       </c>
       <c r="E61" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F61" t="n">
-        <v>22.4489795918367</v>
+        <v>26.530612244898</v>
       </c>
     </row>
     <row r="62">
@@ -2051,13 +2051,13 @@
         <v>47</v>
       </c>
       <c r="D62" t="n">
-        <v>33.7872340425532</v>
+        <v>32.4042553191489</v>
       </c>
       <c r="E62" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="F62" t="n">
-        <v>23.4042553191489</v>
+        <v>34.0425531914894</v>
       </c>
     </row>
     <row r="63">
@@ -2071,13 +2071,13 @@
         <v>45</v>
       </c>
       <c r="D63" t="n">
-        <v>34.2666666666667</v>
+        <v>34.3111111111111</v>
       </c>
       <c r="E63" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F63" t="n">
-        <v>17.7777777777778</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64">
@@ -2091,13 +2091,13 @@
         <v>45</v>
       </c>
       <c r="D64" t="n">
-        <v>34.8666666666667</v>
+        <v>34.2888888888889</v>
       </c>
       <c r="E64" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F64" t="n">
-        <v>20</v>
+        <v>26.6666666666667</v>
       </c>
     </row>
     <row r="65">
@@ -2111,13 +2111,13 @@
         <v>42</v>
       </c>
       <c r="D65" t="n">
-        <v>30.6904761904762</v>
+        <v>29.452380952381</v>
       </c>
       <c r="E65" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F65" t="n">
-        <v>30.952380952381</v>
+        <v>38.0952380952381</v>
       </c>
     </row>
     <row r="66">
@@ -2131,7 +2131,7 @@
         <v>41</v>
       </c>
       <c r="D66" t="n">
-        <v>33.8536585365854</v>
+        <v>33.609756097561</v>
       </c>
       <c r="E66" t="n">
         <v>31</v>
@@ -2151,7 +2151,7 @@
         <v>41</v>
       </c>
       <c r="D67" t="n">
-        <v>36.6585365853659</v>
+        <v>36.5853658536585</v>
       </c>
       <c r="E67" t="n">
         <v>32</v>
@@ -2171,7 +2171,7 @@
         <v>36</v>
       </c>
       <c r="D68" t="n">
-        <v>36.9444444444444</v>
+        <v>36.9722222222222</v>
       </c>
       <c r="E68" t="n">
         <v>35</v>
@@ -2191,7 +2191,7 @@
         <v>35</v>
       </c>
       <c r="D69" t="n">
-        <v>48.6571428571429</v>
+        <v>48.5142857142857</v>
       </c>
       <c r="E69" t="n">
         <v>32</v>
@@ -2211,13 +2211,13 @@
         <v>35</v>
       </c>
       <c r="D70" t="n">
-        <v>32.6285714285714</v>
+        <v>30.7142857142857</v>
       </c>
       <c r="E70" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="F70" t="n">
-        <v>34.2857142857143</v>
+        <v>48.5714285714286</v>
       </c>
     </row>
     <row r="71">
@@ -2231,13 +2231,13 @@
         <v>34</v>
       </c>
       <c r="D71" t="n">
-        <v>31.0588235294118</v>
+        <v>28.6764705882353</v>
       </c>
       <c r="E71" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F71" t="n">
-        <v>41.1764705882353</v>
+        <v>50</v>
       </c>
     </row>
     <row r="72">
@@ -2251,13 +2251,13 @@
         <v>34</v>
       </c>
       <c r="D72" t="n">
-        <v>31.9705882352941</v>
+        <v>30.4117647058824</v>
       </c>
       <c r="E72" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F72" t="n">
-        <v>41.1764705882353</v>
+        <v>50</v>
       </c>
     </row>
     <row r="73">
@@ -2271,13 +2271,13 @@
         <v>34</v>
       </c>
       <c r="D73" t="n">
-        <v>37.9117647058824</v>
+        <v>37.3529411764706</v>
       </c>
       <c r="E73" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F73" t="n">
-        <v>20.5882352941177</v>
+        <v>23.5294117647059</v>
       </c>
     </row>
     <row r="74">
@@ -2291,13 +2291,13 @@
         <v>34</v>
       </c>
       <c r="D74" t="n">
-        <v>33.8529411764706</v>
+        <v>33.0588235294118</v>
       </c>
       <c r="E74" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="F74" t="n">
-        <v>11.7647058823529</v>
+        <v>20.5882352941177</v>
       </c>
     </row>
     <row r="75">
@@ -2311,7 +2311,7 @@
         <v>34</v>
       </c>
       <c r="D75" t="n">
-        <v>34.4705882352941</v>
+        <v>34.0588235294118</v>
       </c>
       <c r="E75" t="n">
         <v>25</v>
@@ -2331,13 +2331,13 @@
         <v>33</v>
       </c>
       <c r="D76" t="n">
-        <v>31.969696969697</v>
+        <v>31.5454545454545</v>
       </c>
       <c r="E76" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F76" t="n">
-        <v>33.3333333333333</v>
+        <v>30.3030303030303</v>
       </c>
     </row>
     <row r="77">
@@ -2351,13 +2351,13 @@
         <v>32</v>
       </c>
       <c r="D77" t="n">
-        <v>33.46875</v>
+        <v>32.9375</v>
       </c>
       <c r="E77" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F77" t="n">
-        <v>25</v>
+        <v>28.125</v>
       </c>
     </row>
     <row r="78">
@@ -2371,7 +2371,7 @@
         <v>32</v>
       </c>
       <c r="D78" t="n">
-        <v>35.5</v>
+        <v>34.65625</v>
       </c>
       <c r="E78" t="n">
         <v>25</v>
@@ -2391,13 +2391,13 @@
         <v>32</v>
       </c>
       <c r="D79" t="n">
-        <v>37.625</v>
+        <v>37.125</v>
       </c>
       <c r="E79" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F79" t="n">
-        <v>9.375</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="80">
@@ -2411,7 +2411,7 @@
         <v>31</v>
       </c>
       <c r="D80" t="n">
-        <v>34.0645161290323</v>
+        <v>34.0322580645161</v>
       </c>
       <c r="E80" t="n">
         <v>23</v>
@@ -2431,13 +2431,13 @@
         <v>29</v>
       </c>
       <c r="D81" t="n">
-        <v>36.7586206896552</v>
+        <v>36.3793103448276</v>
       </c>
       <c r="E81" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F81" t="n">
-        <v>6.89655172413794</v>
+        <v>10.3448275862069</v>
       </c>
     </row>
     <row r="82">
@@ -2451,13 +2451,13 @@
         <v>29</v>
       </c>
       <c r="D82" t="n">
-        <v>34.2413793103448</v>
+        <v>33.9655172413793</v>
       </c>
       <c r="E82" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F82" t="n">
-        <v>17.2413793103448</v>
+        <v>20.6896551724138</v>
       </c>
     </row>
     <row r="83">
@@ -2471,7 +2471,7 @@
         <v>28</v>
       </c>
       <c r="D83" t="n">
-        <v>35.1785714285714</v>
+        <v>34.7142857142857</v>
       </c>
       <c r="E83" t="n">
         <v>22</v>
@@ -2491,7 +2491,7 @@
         <v>27</v>
       </c>
       <c r="D84" t="n">
-        <v>31.2962962962963</v>
+        <v>31.1851851851852</v>
       </c>
       <c r="E84" t="n">
         <v>19</v>
@@ -2511,13 +2511,13 @@
         <v>27</v>
       </c>
       <c r="D85" t="n">
-        <v>34</v>
+        <v>33.7407407407407</v>
       </c>
       <c r="E85" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F85" t="n">
-        <v>22.2222222222222</v>
+        <v>29.6296296296296</v>
       </c>
     </row>
     <row r="86">
@@ -2531,13 +2531,13 @@
         <v>26</v>
       </c>
       <c r="D86" t="n">
-        <v>34.1538461538462</v>
+        <v>34.0384615384615</v>
       </c>
       <c r="E86" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F86" t="n">
-        <v>26.9230769230769</v>
+        <v>23.0769230769231</v>
       </c>
     </row>
     <row r="87">
@@ -2551,13 +2551,13 @@
         <v>26</v>
       </c>
       <c r="D87" t="n">
-        <v>32.5384615384615</v>
+        <v>32.1153846153846</v>
       </c>
       <c r="E87" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F87" t="n">
-        <v>30.7692307692308</v>
+        <v>38.4615384615385</v>
       </c>
     </row>
     <row r="88">
@@ -2571,13 +2571,13 @@
         <v>26</v>
       </c>
       <c r="D88" t="n">
-        <v>42.9615384615385</v>
+        <v>42.5384615384615</v>
       </c>
       <c r="E88" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F88" t="n">
-        <v>3.84615384615384</v>
+        <v>7.69230769230769</v>
       </c>
     </row>
     <row r="89">
@@ -2591,13 +2591,13 @@
         <v>24</v>
       </c>
       <c r="D89" t="n">
-        <v>32.5</v>
+        <v>30.5416666666667</v>
       </c>
       <c r="E89" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F89" t="n">
-        <v>16.6666666666667</v>
+        <v>41.6666666666667</v>
       </c>
     </row>
     <row r="90">
@@ -2611,7 +2611,7 @@
         <v>24</v>
       </c>
       <c r="D90" t="n">
-        <v>33.1666666666667</v>
+        <v>32.875</v>
       </c>
       <c r="E90" t="n">
         <v>16</v>
@@ -2631,13 +2631,13 @@
         <v>24</v>
       </c>
       <c r="D91" t="n">
-        <v>38.3333333333333</v>
+        <v>37</v>
       </c>
       <c r="E91" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F91" t="n">
-        <v>20.8333333333333</v>
+        <v>25</v>
       </c>
     </row>
     <row r="92">
@@ -2651,13 +2651,13 @@
         <v>24</v>
       </c>
       <c r="D92" t="n">
-        <v>31.9166666666667</v>
+        <v>30.5</v>
       </c>
       <c r="E92" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F92" t="n">
-        <v>41.6666666666667</v>
+        <v>45.8333333333333</v>
       </c>
     </row>
     <row r="93">
@@ -2671,13 +2671,13 @@
         <v>23</v>
       </c>
       <c r="D93" t="n">
-        <v>35.4782608695652</v>
+        <v>34.9565217391304</v>
       </c>
       <c r="E93" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F93" t="n">
-        <v>13.0434782608696</v>
+        <v>17.3913043478261</v>
       </c>
     </row>
     <row r="94">
@@ -2691,13 +2691,13 @@
         <v>23</v>
       </c>
       <c r="D94" t="n">
-        <v>31.2173913043478</v>
+        <v>30.9565217391304</v>
       </c>
       <c r="E94" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F94" t="n">
-        <v>30.4347826086957</v>
+        <v>39.1304347826087</v>
       </c>
     </row>
     <row r="95">
@@ -2711,13 +2711,13 @@
         <v>21</v>
       </c>
       <c r="D95" t="n">
-        <v>33.1428571428571</v>
+        <v>30.8095238095238</v>
       </c>
       <c r="E95" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F95" t="n">
-        <v>28.5714285714286</v>
+        <v>38.0952380952381</v>
       </c>
     </row>
     <row r="96">
@@ -2731,7 +2731,7 @@
         <v>21</v>
       </c>
       <c r="D96" t="n">
-        <v>37.3333333333333</v>
+        <v>37.2380952380952</v>
       </c>
       <c r="E96" t="n">
         <v>19</v>
@@ -2751,7 +2751,7 @@
         <v>20</v>
       </c>
       <c r="D97" t="n">
-        <v>33.95</v>
+        <v>33.5</v>
       </c>
       <c r="E97" t="n">
         <v>13</v>
@@ -2771,7 +2771,7 @@
         <v>20</v>
       </c>
       <c r="D98" t="n">
-        <v>37.1</v>
+        <v>36.75</v>
       </c>
       <c r="E98" t="n">
         <v>11</v>
@@ -2791,7 +2791,7 @@
         <v>20</v>
       </c>
       <c r="D99" t="n">
-        <v>36.1</v>
+        <v>35.4</v>
       </c>
       <c r="E99" t="n">
         <v>16</v>
@@ -2811,13 +2811,13 @@
         <v>18</v>
       </c>
       <c r="D100" t="n">
-        <v>34.0555555555556</v>
+        <v>33.9444444444444</v>
       </c>
       <c r="E100" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F100" t="n">
-        <v>27.7777777777778</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="101">
@@ -2831,7 +2831,7 @@
         <v>18</v>
       </c>
       <c r="D101" t="n">
-        <v>33.7777777777778</v>
+        <v>33.3333333333333</v>
       </c>
       <c r="E101" t="n">
         <v>11</v>
@@ -2851,13 +2851,13 @@
         <v>18</v>
       </c>
       <c r="D102" t="n">
-        <v>33.4444444444444</v>
+        <v>33.2777777777778</v>
       </c>
       <c r="E102" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F102" t="n">
-        <v>11.1111111111111</v>
+        <v>16.6666666666667</v>
       </c>
     </row>
     <row r="103">
@@ -2871,7 +2871,7 @@
         <v>17</v>
       </c>
       <c r="D103" t="n">
-        <v>35.0588235294118</v>
+        <v>33.8235294117647</v>
       </c>
       <c r="E103" t="n">
         <v>4</v>
@@ -2891,7 +2891,7 @@
         <v>16</v>
       </c>
       <c r="D104" t="n">
-        <v>32.8125</v>
+        <v>32.375</v>
       </c>
       <c r="E104" t="n">
         <v>10</v>
@@ -2911,7 +2911,7 @@
         <v>16</v>
       </c>
       <c r="D105" t="n">
-        <v>27.25</v>
+        <v>27.125</v>
       </c>
       <c r="E105" t="n">
         <v>5</v>
@@ -2931,13 +2931,13 @@
         <v>16</v>
       </c>
       <c r="D106" t="n">
-        <v>31.375</v>
+        <v>31.125</v>
       </c>
       <c r="E106" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F106" t="n">
-        <v>43.75</v>
+        <v>50</v>
       </c>
     </row>
     <row r="107">
@@ -2951,13 +2951,13 @@
         <v>16</v>
       </c>
       <c r="D107" t="n">
-        <v>38.4375</v>
+        <v>36.125</v>
       </c>
       <c r="E107" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F107" t="n">
-        <v>18.75</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="108">
@@ -2971,7 +2971,7 @@
         <v>16</v>
       </c>
       <c r="D108" t="n">
-        <v>36.3125</v>
+        <v>35.125</v>
       </c>
       <c r="E108" t="n">
         <v>12</v>
@@ -2991,7 +2991,7 @@
         <v>15</v>
       </c>
       <c r="D109" t="n">
-        <v>37.9333333333333</v>
+        <v>38.8666666666667</v>
       </c>
       <c r="E109" t="n">
         <v>10</v>
@@ -3011,13 +3011,13 @@
         <v>15</v>
       </c>
       <c r="D110" t="n">
-        <v>28.3333333333333</v>
+        <v>27.5333333333333</v>
       </c>
       <c r="E110" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F110" t="n">
-        <v>60</v>
+        <v>73.3333333333333</v>
       </c>
     </row>
     <row r="111">
@@ -3031,13 +3031,13 @@
         <v>14</v>
       </c>
       <c r="D111" t="n">
-        <v>31.7857142857143</v>
+        <v>31.4285714285714</v>
       </c>
       <c r="E111" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F111" t="n">
-        <v>35.7142857142857</v>
+        <v>42.8571428571429</v>
       </c>
     </row>
     <row r="112">
@@ -3051,13 +3051,13 @@
         <v>14</v>
       </c>
       <c r="D112" t="n">
-        <v>30.9285714285714</v>
+        <v>30.8571428571429</v>
       </c>
       <c r="E112" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F112" t="n">
-        <v>35.7142857142857</v>
+        <v>42.8571428571429</v>
       </c>
     </row>
     <row r="113">
@@ -3071,7 +3071,7 @@
         <v>13</v>
       </c>
       <c r="D113" t="n">
-        <v>38</v>
+        <v>37.6923076923077</v>
       </c>
       <c r="E113" t="n">
         <v>7</v>
@@ -3111,7 +3111,7 @@
         <v>11</v>
       </c>
       <c r="D115" t="n">
-        <v>32.2727272727273</v>
+        <v>31.3636363636364</v>
       </c>
       <c r="E115" t="n">
         <v>5</v>
@@ -3131,7 +3131,7 @@
         <v>11</v>
       </c>
       <c r="D116" t="n">
-        <v>29.5454545454545</v>
+        <v>29.4545454545455</v>
       </c>
       <c r="E116" t="n">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>11</v>
       </c>
       <c r="D117" t="n">
-        <v>41.6363636363636</v>
+        <v>39.0909090909091</v>
       </c>
       <c r="E117" t="n">
         <v>8</v>
@@ -3171,7 +3171,7 @@
         <v>10</v>
       </c>
       <c r="D118" t="n">
-        <v>35.2</v>
+        <v>33.2</v>
       </c>
       <c r="E118" t="n">
         <v>8</v>
@@ -3191,7 +3191,7 @@
         <v>10</v>
       </c>
       <c r="D119" t="n">
-        <v>34.6</v>
+        <v>34.3</v>
       </c>
       <c r="E119" t="n">
         <v>8</v>
@@ -3211,13 +3211,13 @@
         <v>10</v>
       </c>
       <c r="D120" t="n">
-        <v>33.2</v>
+        <v>30.7</v>
       </c>
       <c r="E120" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F120" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="121">
@@ -3231,13 +3231,13 @@
         <v>9</v>
       </c>
       <c r="D121" t="n">
-        <v>30.7777777777778</v>
+        <v>29.4444444444444</v>
       </c>
       <c r="E121" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F121" t="n">
-        <v>44.4444444444444</v>
+        <v>55.5555555555556</v>
       </c>
     </row>
     <row r="122">
@@ -3271,7 +3271,7 @@
         <v>8</v>
       </c>
       <c r="D123" t="n">
-        <v>28.375</v>
+        <v>28.25</v>
       </c>
       <c r="E123" t="n">
         <v>4</v>
@@ -3291,7 +3291,7 @@
         <v>8</v>
       </c>
       <c r="D124" t="n">
-        <v>35.5</v>
+        <v>35.25</v>
       </c>
       <c r="E124" t="n">
         <v>6</v>
@@ -3311,7 +3311,7 @@
         <v>8</v>
       </c>
       <c r="D125" t="n">
-        <v>41.5</v>
+        <v>41.375</v>
       </c>
       <c r="E125" t="n">
         <v>6</v>
@@ -3331,13 +3331,13 @@
         <v>8</v>
       </c>
       <c r="D126" t="n">
-        <v>28.75</v>
+        <v>27</v>
       </c>
       <c r="E126" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F126" t="n">
-        <v>25</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="127">
@@ -3391,13 +3391,13 @@
         <v>6</v>
       </c>
       <c r="D129" t="n">
-        <v>38.6666666666667</v>
+        <v>38.5</v>
       </c>
       <c r="E129" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F129" t="n">
-        <v>16.6666666666667</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="130">
@@ -3411,7 +3411,7 @@
         <v>6</v>
       </c>
       <c r="D130" t="n">
-        <v>30.3333333333333</v>
+        <v>28.8333333333333</v>
       </c>
       <c r="E130" t="n">
         <v>2</v>
@@ -3431,13 +3431,13 @@
         <v>5</v>
       </c>
       <c r="D131" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="E131" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F131" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="132">
@@ -3451,7 +3451,7 @@
         <v>5</v>
       </c>
       <c r="D132" t="n">
-        <v>32.2</v>
+        <v>31.2</v>
       </c>
       <c r="E132" t="n">
         <v>3</v>
@@ -3471,13 +3471,13 @@
         <v>5</v>
       </c>
       <c r="D133" t="n">
-        <v>36</v>
+        <v>34.4</v>
       </c>
       <c r="E133" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F133" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
     </row>
     <row r="134">
@@ -3511,7 +3511,7 @@
         <v>4</v>
       </c>
       <c r="D135" t="n">
-        <v>48.75</v>
+        <v>47.5</v>
       </c>
       <c r="E135" t="n">
         <v>4</v>
@@ -3531,7 +3531,7 @@
         <v>4</v>
       </c>
       <c r="D136" t="n">
-        <v>35.25</v>
+        <v>30.5</v>
       </c>
       <c r="E136" t="n">
         <v>3</v>
@@ -3591,7 +3591,7 @@
         <v>3</v>
       </c>
       <c r="D139" t="n">
-        <v>31.3333333333333</v>
+        <v>30.3333333333333</v>
       </c>
       <c r="E139" t="n">
         <v>2</v>
@@ -3671,7 +3671,7 @@
         <v>3</v>
       </c>
       <c r="D143" t="n">
-        <v>28.6666666666667</v>
+        <v>28.3333333333333</v>
       </c>
       <c r="E143" t="n">
         <v>1</v>
@@ -3691,7 +3691,7 @@
         <v>3</v>
       </c>
       <c r="D144" t="n">
-        <v>27.3333333333333</v>
+        <v>25.3333333333333</v>
       </c>
       <c r="E144" t="n">
         <v>2</v>
@@ -3731,7 +3731,7 @@
         <v>2</v>
       </c>
       <c r="D146" t="n">
-        <v>35.5</v>
+        <v>34.5</v>
       </c>
       <c r="E146" t="n">
         <v>1</v>
@@ -3791,7 +3791,7 @@
         <v>2</v>
       </c>
       <c r="D149" t="n">
-        <v>24.5</v>
+        <v>24</v>
       </c>
       <c r="E149" t="n">
         <v>1</v>
@@ -3851,7 +3851,7 @@
         <v>1</v>
       </c>
       <c r="D152" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="E152" t="n">
         <v>1</v>
@@ -3911,13 +3911,13 @@
         <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="E155" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F155" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -4154,13 +4154,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D20B2F4E-A985-4B50-9FB1-9CBB73E96E56}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D307036-B070-413F-BE07-EACD8C4CC124}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{73294184-E9D1-4DCD-9C7E-8175A03869C0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D193F08-196C-4CE7-AFF0-E973B201203D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F815A132-BD60-4ABF-A284-57A91583D282}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E25C9FAE-7F23-4DD4-8C94-C22908AFD9F5}"/>
 </file>
--- a/data/WP18/WP18_auswertung_sachgebiete.xlsx
+++ b/data/WP18/WP18_auswertung_sachgebiete.xlsx
@@ -854,10 +854,10 @@
         <v>36.8541202672606</v>
       </c>
       <c r="E2" t="n">
-        <v>1404</v>
+        <v>1508</v>
       </c>
       <c r="F2" t="n">
-        <v>21.826280623608</v>
+        <v>16.0356347438753</v>
       </c>
     </row>
     <row r="3">
@@ -874,10 +874,10 @@
         <v>39.3333333333333</v>
       </c>
       <c r="E3" t="n">
-        <v>631</v>
+        <v>664</v>
       </c>
       <c r="F3" t="n">
-        <v>16.8642951251647</v>
+        <v>12.5164690382082</v>
       </c>
     </row>
     <row r="4">
@@ -894,10 +894,10 @@
         <v>35.6943005181347</v>
       </c>
       <c r="E4" t="n">
-        <v>483</v>
+        <v>504</v>
       </c>
       <c r="F4" t="n">
-        <v>16.580310880829</v>
+        <v>12.9533678756477</v>
       </c>
     </row>
     <row r="5">
@@ -914,10 +914,10 @@
         <v>34.137330754352</v>
       </c>
       <c r="E5" t="n">
-        <v>304</v>
+        <v>335</v>
       </c>
       <c r="F5" t="n">
-        <v>41.1992263056093</v>
+        <v>35.2030947775629</v>
       </c>
     </row>
     <row r="6">
@@ -934,10 +934,10 @@
         <v>35.5288888888889</v>
       </c>
       <c r="E6" t="n">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="F6" t="n">
-        <v>21.1111111111111</v>
+        <v>18.6666666666667</v>
       </c>
     </row>
     <row r="7">
@@ -954,10 +954,10 @@
         <v>39.1240506329114</v>
       </c>
       <c r="E7" t="n">
-        <v>316</v>
+        <v>336</v>
       </c>
       <c r="F7" t="n">
-        <v>20</v>
+        <v>14.9367088607595</v>
       </c>
     </row>
     <row r="8">
@@ -974,10 +974,10 @@
         <v>35.8097826086956</v>
       </c>
       <c r="E8" t="n">
-        <v>310</v>
+        <v>324</v>
       </c>
       <c r="F8" t="n">
-        <v>15.7608695652174</v>
+        <v>11.9565217391304</v>
       </c>
     </row>
     <row r="9">
@@ -994,10 +994,10 @@
         <v>32.8121546961326</v>
       </c>
       <c r="E9" t="n">
-        <v>230</v>
+        <v>251</v>
       </c>
       <c r="F9" t="n">
-        <v>36.46408839779</v>
+        <v>30.6629834254144</v>
       </c>
     </row>
     <row r="10">
@@ -1014,10 +1014,10 @@
         <v>36.4375</v>
       </c>
       <c r="E10" t="n">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="F10" t="n">
-        <v>25.2840909090909</v>
+        <v>20.7386363636364</v>
       </c>
     </row>
     <row r="11">
@@ -1034,10 +1034,10 @@
         <v>38.9019607843137</v>
       </c>
       <c r="E11" t="n">
-        <v>253</v>
+        <v>267</v>
       </c>
       <c r="F11" t="n">
-        <v>17.3202614379085</v>
+        <v>12.7450980392157</v>
       </c>
     </row>
     <row r="12">
@@ -1054,10 +1054,10 @@
         <v>30.4700854700855</v>
       </c>
       <c r="E12" t="n">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="F12" t="n">
-        <v>61.965811965812</v>
+        <v>51.7094017094017</v>
       </c>
     </row>
     <row r="13">
@@ -1074,10 +1074,10 @@
         <v>30.5566502463054</v>
       </c>
       <c r="E13" t="n">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="F13" t="n">
-        <v>35.4679802955665</v>
+        <v>27.0935960591133</v>
       </c>
     </row>
     <row r="14">
@@ -1094,10 +1094,10 @@
         <v>30.4723618090452</v>
       </c>
       <c r="E14" t="n">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="F14" t="n">
-        <v>54.2713567839196</v>
+        <v>42.713567839196</v>
       </c>
     </row>
     <row r="15">
@@ -1114,10 +1114,10 @@
         <v>35.5882352941176</v>
       </c>
       <c r="E15" t="n">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="F15" t="n">
-        <v>28.3422459893048</v>
+        <v>23.5294117647059</v>
       </c>
     </row>
     <row r="16">
@@ -1134,10 +1134,10 @@
         <v>32.0384615384615</v>
       </c>
       <c r="E16" t="n">
-        <v>106</v>
+        <v>150</v>
       </c>
       <c r="F16" t="n">
-        <v>41.7582417582418</v>
+        <v>17.5824175824176</v>
       </c>
     </row>
     <row r="17">
@@ -1154,10 +1154,10 @@
         <v>34.3181818181818</v>
       </c>
       <c r="E17" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="F17" t="n">
-        <v>24.4318181818182</v>
+        <v>19.8863636363636</v>
       </c>
     </row>
     <row r="18">
@@ -1174,10 +1174,10 @@
         <v>33.222972972973</v>
       </c>
       <c r="E18" t="n">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="F18" t="n">
-        <v>34.4594594594595</v>
+        <v>27.7027027027027</v>
       </c>
     </row>
     <row r="19">
@@ -1194,10 +1194,10 @@
         <v>29.0518518518519</v>
       </c>
       <c r="E19" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F19" t="n">
-        <v>48.8888888888889</v>
+        <v>44.4444444444444</v>
       </c>
     </row>
     <row r="20">
@@ -1214,10 +1214,10 @@
         <v>30.6616541353383</v>
       </c>
       <c r="E20" t="n">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="F20" t="n">
-        <v>39.8496240601504</v>
+        <v>26.3157894736842</v>
       </c>
     </row>
     <row r="21">
@@ -1234,10 +1234,10 @@
         <v>36.9160305343511</v>
       </c>
       <c r="E21" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="F21" t="n">
-        <v>22.9007633587786</v>
+        <v>17.557251908397</v>
       </c>
     </row>
     <row r="22">
@@ -1254,10 +1254,10 @@
         <v>30.1484375</v>
       </c>
       <c r="E22" t="n">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="F22" t="n">
-        <v>32.8125</v>
+        <v>21.875</v>
       </c>
     </row>
     <row r="23">
@@ -1274,10 +1274,10 @@
         <v>40.546875</v>
       </c>
       <c r="E23" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F23" t="n">
-        <v>8.59375</v>
+        <v>7.03125</v>
       </c>
     </row>
     <row r="24">
@@ -1294,10 +1294,10 @@
         <v>37.1338582677165</v>
       </c>
       <c r="E24" t="n">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="F24" t="n">
-        <v>18.8976377952756</v>
+        <v>13.3858267716535</v>
       </c>
     </row>
     <row r="25">
@@ -1314,10 +1314,10 @@
         <v>39.9516129032258</v>
       </c>
       <c r="E25" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F25" t="n">
-        <v>12.0967741935484</v>
+        <v>9.67741935483872</v>
       </c>
     </row>
     <row r="26">
@@ -1334,10 +1334,10 @@
         <v>34.6666666666667</v>
       </c>
       <c r="E26" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="F26" t="n">
-        <v>14.5299145299145</v>
+        <v>10.2564102564102</v>
       </c>
     </row>
     <row r="27">
@@ -1354,10 +1354,10 @@
         <v>33.6548672566372</v>
       </c>
       <c r="E27" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F27" t="n">
-        <v>20.353982300885</v>
+        <v>18.5840707964602</v>
       </c>
     </row>
     <row r="28">
@@ -1374,10 +1374,10 @@
         <v>35.2909090909091</v>
       </c>
       <c r="E28" t="n">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F28" t="n">
-        <v>26.3636363636364</v>
+        <v>20</v>
       </c>
     </row>
     <row r="29">
@@ -1394,10 +1394,10 @@
         <v>34.2577319587629</v>
       </c>
       <c r="E29" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="F29" t="n">
-        <v>25.7731958762887</v>
+        <v>19.5876288659794</v>
       </c>
     </row>
     <row r="30">
@@ -1414,10 +1414,10 @@
         <v>34.4479166666667</v>
       </c>
       <c r="E30" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="F30" t="n">
-        <v>29.1666666666667</v>
+        <v>21.875</v>
       </c>
     </row>
     <row r="31">
@@ -1434,10 +1434,10 @@
         <v>35.7578947368421</v>
       </c>
       <c r="E31" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F31" t="n">
-        <v>22.1052631578947</v>
+        <v>16.8421052631579</v>
       </c>
     </row>
     <row r="32">
@@ -1454,10 +1454,10 @@
         <v>32.5578947368421</v>
       </c>
       <c r="E32" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="F32" t="n">
-        <v>37.8947368421053</v>
+        <v>29.4736842105263</v>
       </c>
     </row>
     <row r="33">
@@ -1474,10 +1474,10 @@
         <v>35.1397849462366</v>
       </c>
       <c r="E33" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F33" t="n">
-        <v>25.8064516129032</v>
+        <v>21.505376344086</v>
       </c>
     </row>
     <row r="34">
@@ -1494,10 +1494,10 @@
         <v>38.6373626373626</v>
       </c>
       <c r="E34" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F34" t="n">
-        <v>23.0769230769231</v>
+        <v>21.978021978022</v>
       </c>
     </row>
     <row r="35">
@@ -1534,10 +1534,10 @@
         <v>30.1460674157303</v>
       </c>
       <c r="E36" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F36" t="n">
-        <v>57.3033707865169</v>
+        <v>34.8314606741573</v>
       </c>
     </row>
     <row r="37">
@@ -1554,10 +1554,10 @@
         <v>32.6741573033708</v>
       </c>
       <c r="E37" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="F37" t="n">
-        <v>24.7191011235955</v>
+        <v>17.9775280898876</v>
       </c>
     </row>
     <row r="38">
@@ -1574,10 +1574,10 @@
         <v>36.4886363636364</v>
       </c>
       <c r="E38" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F38" t="n">
-        <v>25</v>
+        <v>18.1818181818182</v>
       </c>
     </row>
     <row r="39">
@@ -1594,10 +1594,10 @@
         <v>29.4367816091954</v>
       </c>
       <c r="E39" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="F39" t="n">
-        <v>72.4137931034483</v>
+        <v>55.1724137931034</v>
       </c>
     </row>
     <row r="40">
@@ -1614,10 +1614,10 @@
         <v>33.6941176470588</v>
       </c>
       <c r="E40" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F40" t="n">
-        <v>27.0588235294118</v>
+        <v>21.1764705882353</v>
       </c>
     </row>
     <row r="41">
@@ -1634,10 +1634,10 @@
         <v>33.6385542168675</v>
       </c>
       <c r="E41" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F41" t="n">
-        <v>30.1204819277108</v>
+        <v>24.0963855421687</v>
       </c>
     </row>
     <row r="42">
@@ -1654,10 +1654,10 @@
         <v>28.9036144578313</v>
       </c>
       <c r="E42" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="F42" t="n">
-        <v>74.6987951807229</v>
+        <v>57.8313253012048</v>
       </c>
     </row>
     <row r="43">
@@ -1674,10 +1674,10 @@
         <v>40.4146341463415</v>
       </c>
       <c r="E43" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F43" t="n">
-        <v>4.8780487804878</v>
+        <v>3.65853658536585</v>
       </c>
     </row>
     <row r="44">
@@ -1694,10 +1694,10 @@
         <v>37.0493827160494</v>
       </c>
       <c r="E44" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F44" t="n">
-        <v>18.5185185185185</v>
+        <v>14.8148148148148</v>
       </c>
     </row>
     <row r="45">
@@ -1714,10 +1714,10 @@
         <v>34.0897435897436</v>
       </c>
       <c r="E45" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F45" t="n">
-        <v>30.7692307692308</v>
+        <v>23.0769230769231</v>
       </c>
     </row>
     <row r="46">
@@ -1734,10 +1734,10 @@
         <v>34.8589743589744</v>
       </c>
       <c r="E46" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="F46" t="n">
-        <v>32.051282051282</v>
+        <v>24.3589743589744</v>
       </c>
     </row>
     <row r="47">
@@ -1754,10 +1754,10 @@
         <v>36.025974025974</v>
       </c>
       <c r="E47" t="n">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="F47" t="n">
-        <v>24.6753246753247</v>
+        <v>12.987012987013</v>
       </c>
     </row>
     <row r="48">
@@ -1774,10 +1774,10 @@
         <v>35.75</v>
       </c>
       <c r="E48" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="F48" t="n">
-        <v>39.4736842105263</v>
+        <v>27.6315789473684</v>
       </c>
     </row>
     <row r="49">
@@ -1794,10 +1794,10 @@
         <v>34.8888888888889</v>
       </c>
       <c r="E49" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F49" t="n">
-        <v>19.4444444444444</v>
+        <v>16.6666666666667</v>
       </c>
     </row>
     <row r="50">
@@ -1814,10 +1814,10 @@
         <v>35.1617647058824</v>
       </c>
       <c r="E50" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="F50" t="n">
-        <v>16.1764705882353</v>
+        <v>8.82352941176471</v>
       </c>
     </row>
     <row r="51">
@@ -1834,10 +1834,10 @@
         <v>40.5074626865672</v>
       </c>
       <c r="E51" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F51" t="n">
-        <v>11.9402985074627</v>
+        <v>8.95522388059702</v>
       </c>
     </row>
     <row r="52">
@@ -1854,10 +1854,10 @@
         <v>33.2258064516129</v>
       </c>
       <c r="E52" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F52" t="n">
-        <v>30.6451612903226</v>
+        <v>24.1935483870968</v>
       </c>
     </row>
     <row r="53">
@@ -1874,10 +1874,10 @@
         <v>35.5833333333333</v>
       </c>
       <c r="E53" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F53" t="n">
-        <v>30</v>
+        <v>28.3333333333333</v>
       </c>
     </row>
     <row r="54">
@@ -1894,10 +1894,10 @@
         <v>37.2333333333333</v>
       </c>
       <c r="E54" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F54" t="n">
-        <v>11.6666666666667</v>
+        <v>8.33333333333334</v>
       </c>
     </row>
     <row r="55">
@@ -1914,10 +1914,10 @@
         <v>37.3928571428571</v>
       </c>
       <c r="E55" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="F55" t="n">
-        <v>23.2142857142857</v>
+        <v>16.0714285714286</v>
       </c>
     </row>
     <row r="56">
@@ -1934,10 +1934,10 @@
         <v>36.9285714285714</v>
       </c>
       <c r="E56" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F56" t="n">
-        <v>16.0714285714286</v>
+        <v>10.7142857142857</v>
       </c>
     </row>
     <row r="57">
@@ -1954,10 +1954,10 @@
         <v>29.9622641509434</v>
       </c>
       <c r="E57" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F57" t="n">
-        <v>49.0566037735849</v>
+        <v>35.8490566037736</v>
       </c>
     </row>
     <row r="58">
@@ -1974,10 +1974,10 @@
         <v>33.1730769230769</v>
       </c>
       <c r="E58" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F58" t="n">
-        <v>30.7692307692308</v>
+        <v>23.0769230769231</v>
       </c>
     </row>
     <row r="59">
@@ -2014,10 +2014,10 @@
         <v>38.3469387755102</v>
       </c>
       <c r="E60" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F60" t="n">
-        <v>30.6122448979592</v>
+        <v>22.4489795918367</v>
       </c>
     </row>
     <row r="61">
@@ -2034,10 +2034,10 @@
         <v>35.3469387755102</v>
       </c>
       <c r="E61" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F61" t="n">
-        <v>26.530612244898</v>
+        <v>20.4081632653061</v>
       </c>
     </row>
     <row r="62">
@@ -2074,10 +2074,10 @@
         <v>34.3111111111111</v>
       </c>
       <c r="E63" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F63" t="n">
-        <v>20</v>
+        <v>15.5555555555556</v>
       </c>
     </row>
     <row r="64">
@@ -2094,10 +2094,10 @@
         <v>34.2888888888889</v>
       </c>
       <c r="E64" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="F64" t="n">
-        <v>26.6666666666667</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65">
@@ -2134,10 +2134,10 @@
         <v>33.609756097561</v>
       </c>
       <c r="E66" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F66" t="n">
-        <v>24.390243902439</v>
+        <v>17.0731707317073</v>
       </c>
     </row>
     <row r="67">
@@ -2154,10 +2154,10 @@
         <v>36.5853658536585</v>
       </c>
       <c r="E67" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F67" t="n">
-        <v>21.9512195121951</v>
+        <v>17.0731707317073</v>
       </c>
     </row>
     <row r="68">
@@ -2194,10 +2194,10 @@
         <v>48.5142857142857</v>
       </c>
       <c r="E69" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F69" t="n">
-        <v>8.57142857142857</v>
+        <v>5.71428571428572</v>
       </c>
     </row>
     <row r="70">
@@ -2214,10 +2214,10 @@
         <v>30.7142857142857</v>
       </c>
       <c r="E70" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F70" t="n">
-        <v>48.5714285714286</v>
+        <v>34.2857142857143</v>
       </c>
     </row>
     <row r="71">
@@ -2234,10 +2234,10 @@
         <v>28.6764705882353</v>
       </c>
       <c r="E71" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F71" t="n">
-        <v>50</v>
+        <v>38.2352941176471</v>
       </c>
     </row>
     <row r="72">
@@ -2254,10 +2254,10 @@
         <v>30.4117647058824</v>
       </c>
       <c r="E72" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F72" t="n">
-        <v>50</v>
+        <v>32.3529411764706</v>
       </c>
     </row>
     <row r="73">
@@ -2274,10 +2274,10 @@
         <v>37.3529411764706</v>
       </c>
       <c r="E73" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F73" t="n">
-        <v>23.5294117647059</v>
+        <v>14.7058823529412</v>
       </c>
     </row>
     <row r="74">
@@ -2294,10 +2294,10 @@
         <v>33.0588235294118</v>
       </c>
       <c r="E74" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F74" t="n">
-        <v>20.5882352941177</v>
+        <v>11.7647058823529</v>
       </c>
     </row>
     <row r="75">
@@ -2354,10 +2354,10 @@
         <v>32.9375</v>
       </c>
       <c r="E77" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F77" t="n">
-        <v>28.125</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="78">
@@ -2374,10 +2374,10 @@
         <v>34.65625</v>
       </c>
       <c r="E78" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F78" t="n">
-        <v>21.875</v>
+        <v>15.625</v>
       </c>
     </row>
     <row r="79">
@@ -2414,10 +2414,10 @@
         <v>34.0322580645161</v>
       </c>
       <c r="E80" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F80" t="n">
-        <v>25.8064516129032</v>
+        <v>22.5806451612903</v>
       </c>
     </row>
     <row r="81">
@@ -2434,10 +2434,10 @@
         <v>36.3793103448276</v>
       </c>
       <c r="E81" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F81" t="n">
-        <v>10.3448275862069</v>
+        <v>6.89655172413794</v>
       </c>
     </row>
     <row r="82">
@@ -2454,10 +2454,10 @@
         <v>33.9655172413793</v>
       </c>
       <c r="E82" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F82" t="n">
-        <v>20.6896551724138</v>
+        <v>10.3448275862069</v>
       </c>
     </row>
     <row r="83">
@@ -2474,10 +2474,10 @@
         <v>34.7142857142857</v>
       </c>
       <c r="E83" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F83" t="n">
-        <v>21.4285714285714</v>
+        <v>7.14285714285714</v>
       </c>
     </row>
     <row r="84">
@@ -2494,10 +2494,10 @@
         <v>31.1851851851852</v>
       </c>
       <c r="E84" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F84" t="n">
-        <v>29.6296296296296</v>
+        <v>22.2222222222222</v>
       </c>
     </row>
     <row r="85">
@@ -2534,10 +2534,10 @@
         <v>34.0384615384615</v>
       </c>
       <c r="E86" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F86" t="n">
-        <v>23.0769230769231</v>
+        <v>19.2307692307692</v>
       </c>
     </row>
     <row r="87">
@@ -2554,10 +2554,10 @@
         <v>32.1153846153846</v>
       </c>
       <c r="E87" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F87" t="n">
-        <v>38.4615384615385</v>
+        <v>26.9230769230769</v>
       </c>
     </row>
     <row r="88">
@@ -2574,10 +2574,10 @@
         <v>42.5384615384615</v>
       </c>
       <c r="E88" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F88" t="n">
-        <v>7.69230769230769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89">
@@ -2594,10 +2594,10 @@
         <v>30.5416666666667</v>
       </c>
       <c r="E89" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F89" t="n">
-        <v>41.6666666666667</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="90">
@@ -2614,10 +2614,10 @@
         <v>32.875</v>
       </c>
       <c r="E90" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F90" t="n">
-        <v>33.3333333333333</v>
+        <v>29.1666666666667</v>
       </c>
     </row>
     <row r="91">
@@ -2634,10 +2634,10 @@
         <v>37</v>
       </c>
       <c r="E91" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F91" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="92">
@@ -2654,10 +2654,10 @@
         <v>30.5</v>
       </c>
       <c r="E92" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F92" t="n">
-        <v>45.8333333333333</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="93">
@@ -2674,10 +2674,10 @@
         <v>34.9565217391304</v>
       </c>
       <c r="E93" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F93" t="n">
-        <v>17.3913043478261</v>
+        <v>13.0434782608696</v>
       </c>
     </row>
     <row r="94">
@@ -2694,10 +2694,10 @@
         <v>30.9565217391304</v>
       </c>
       <c r="E94" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F94" t="n">
-        <v>39.1304347826087</v>
+        <v>26.0869565217391</v>
       </c>
     </row>
     <row r="95">
@@ -2754,10 +2754,10 @@
         <v>33.5</v>
       </c>
       <c r="E97" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F97" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="98">
@@ -2774,10 +2774,10 @@
         <v>36.75</v>
       </c>
       <c r="E98" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F98" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="99">
@@ -2834,10 +2834,10 @@
         <v>33.3333333333333</v>
       </c>
       <c r="E101" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F101" t="n">
-        <v>38.8888888888889</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="102">
@@ -2874,10 +2874,10 @@
         <v>33.8235294117647</v>
       </c>
       <c r="E103" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F103" t="n">
-        <v>76.4705882352941</v>
+        <v>64.7058823529412</v>
       </c>
     </row>
     <row r="104">
@@ -2914,10 +2914,10 @@
         <v>27.125</v>
       </c>
       <c r="E105" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F105" t="n">
-        <v>68.75</v>
+        <v>56.25</v>
       </c>
     </row>
     <row r="106">
@@ -2994,10 +2994,10 @@
         <v>38.8666666666667</v>
       </c>
       <c r="E109" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F109" t="n">
-        <v>33.3333333333333</v>
+        <v>20</v>
       </c>
     </row>
     <row r="110">
@@ -3014,10 +3014,10 @@
         <v>27.5333333333333</v>
       </c>
       <c r="E110" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F110" t="n">
-        <v>73.3333333333333</v>
+        <v>53.3333333333333</v>
       </c>
     </row>
     <row r="111">
@@ -3034,10 +3034,10 @@
         <v>31.4285714285714</v>
       </c>
       <c r="E111" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F111" t="n">
-        <v>42.8571428571429</v>
+        <v>28.5714285714286</v>
       </c>
     </row>
     <row r="112">
@@ -3054,10 +3054,10 @@
         <v>30.8571428571429</v>
       </c>
       <c r="E112" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F112" t="n">
-        <v>42.8571428571429</v>
+        <v>21.4285714285714</v>
       </c>
     </row>
     <row r="113">
@@ -3074,10 +3074,10 @@
         <v>37.6923076923077</v>
       </c>
       <c r="E113" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F113" t="n">
-        <v>46.1538461538462</v>
+        <v>23.0769230769231</v>
       </c>
     </row>
     <row r="114">
@@ -3114,10 +3114,10 @@
         <v>31.3636363636364</v>
       </c>
       <c r="E115" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F115" t="n">
-        <v>54.5454545454545</v>
+        <v>27.2727272727273</v>
       </c>
     </row>
     <row r="116">
@@ -3234,10 +3234,10 @@
         <v>29.4444444444444</v>
       </c>
       <c r="E121" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F121" t="n">
-        <v>55.5555555555556</v>
+        <v>44.4444444444444</v>
       </c>
     </row>
     <row r="122">
@@ -3254,10 +3254,10 @@
         <v>30</v>
       </c>
       <c r="E122" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F122" t="n">
-        <v>33.3333333333333</v>
+        <v>22.2222222222222</v>
       </c>
     </row>
     <row r="123">
@@ -3294,10 +3294,10 @@
         <v>35.25</v>
       </c>
       <c r="E124" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F124" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="125">
@@ -3374,10 +3374,10 @@
         <v>40.8333333333333</v>
       </c>
       <c r="E128" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F128" t="n">
-        <v>33.3333333333333</v>
+        <v>16.6666666666667</v>
       </c>
     </row>
     <row r="129">
@@ -3394,10 +3394,10 @@
         <v>38.5</v>
       </c>
       <c r="E129" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F129" t="n">
-        <v>33.3333333333333</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130">
@@ -3434,10 +3434,10 @@
         <v>36</v>
       </c>
       <c r="E131" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F131" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3474,10 +3474,10 @@
         <v>34.4</v>
       </c>
       <c r="E133" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F133" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134">
@@ -3494,10 +3494,10 @@
         <v>33.4</v>
       </c>
       <c r="E134" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F134" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="135">
@@ -3614,10 +3614,10 @@
         <v>32.6666666666667</v>
       </c>
       <c r="E140" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F140" t="n">
-        <v>66.6666666666667</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141">
@@ -3674,10 +3674,10 @@
         <v>28.3333333333333</v>
       </c>
       <c r="E143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F143" t="n">
-        <v>66.6666666666667</v>
+        <v>33.3333333333333</v>
       </c>
     </row>
     <row r="144">
@@ -3834,10 +3834,10 @@
         <v>28</v>
       </c>
       <c r="E151" t="n">
+        <v>1</v>
+      </c>
+      <c r="F151" t="n">
         <v>0</v>
-      </c>
-      <c r="F151" t="n">
-        <v>100</v>
       </c>
     </row>
     <row r="152">
@@ -3914,10 +3914,10 @@
         <v>28</v>
       </c>
       <c r="E155" t="n">
+        <v>1</v>
+      </c>
+      <c r="F155" t="n">
         <v>0</v>
-      </c>
-      <c r="F155" t="n">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -4154,13 +4154,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D307036-B070-413F-BE07-EACD8C4CC124}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F5D1E634-5AF2-4271-A7F9-C410AC26623C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6D193F08-196C-4CE7-AFF0-E973B201203D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAA3758F-D674-4556-8F9C-CFB7B3EDC78D}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E25C9FAE-7F23-4DD4-8C94-C22908AFD9F5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{697D859B-2390-48DC-989E-A0A8A7935282}"/>
 </file>